--- a/excel/Twino.xlsx
+++ b/excel/Twino.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Twino\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Twino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D4E069-6E7F-416D-AB73-9CD69145A730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E6E1EC-10AE-45FE-81DE-495C4DAF4BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K3" s="19">
         <f ca="1">LVX0000VCV76!B12</f>
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="L3" s="19" t="str">
         <f ca="1">LVX0000VCV76!P3</f>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="N3" s="3">
         <f>LVX0000VCV76!L3</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O3" s="3">
         <f>LVX0000VCV76!M3</f>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="T3" s="29">
         <f>W3-R3</f>
-        <v>3.0000000000001137E-2</v>
+        <v>0.16000000000000014</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M93)</f>
@@ -1243,27 +1243,27 @@
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N93)-AA3</f>
-        <v>0.03</v>
+        <v>0.16000000000000003</v>
       </c>
       <c r="W3" s="29">
         <f>Q3+V3+S3</f>
-        <v>30.03</v>
+        <v>30.16</v>
       </c>
       <c r="X3" s="29">
         <f>W3-Q3</f>
-        <v>3.0000000000001137E-2</v>
+        <v>0.16000000000000014</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>1.000000000000038E-3</v>
+        <v>5.3333333333333384E-3</v>
       </c>
       <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>2.2494205832481386E-2</v>
+        <v>4.2730233073234564E-2</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O93)</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">LVX0000VCV76!Z3</f>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K4" s="19">
         <f ca="1">LVX0000VAUM7!B12</f>
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="L4" s="19" t="str">
         <f ca="1">LVX0000VAUM7!P3</f>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K5" s="19">
         <f ca="1">LVX0000R1N56!B12</f>
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="L5" s="19" t="str">
         <f ca="1">LVX0000R1N56!P3</f>
@@ -1401,11 +1401,11 @@
       </c>
       <c r="N5" s="3">
         <f>LVX0000R1N56!L3</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O5" s="3">
         <f>LVX0000R1N56!M3</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
@@ -3194,14 +3194,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>30.03</v>
+        <v>30.16</v>
       </c>
     </row>
   </sheetData>
@@ -3327,14 +3327,22 @@
       <c r="D3" s="11">
         <v>46273</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="19" t="str">
+      <c r="E3" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>-1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -3342,11 +3350,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -3399,11 +3407,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3587,7 +3595,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -4452,11 +4460,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -4682,9 +4690,9 @@
         <f>IF(E4&gt;0,E4-D4,"")</f>
         <v/>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -4880,7 +4888,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -5901,14 +5909,22 @@
       <c r="D3" s="11">
         <v>46274</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="19" t="str">
+      <c r="E3" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>-2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -5916,7 +5932,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -5973,11 +5989,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -6171,7 +6187,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="D12" s="11">
         <v>46547</v>
@@ -7041,7 +7057,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
